--- a/05-inferencia/data/poblacion-indigena-region.xlsx
+++ b/05-inferencia/data/poblacion-indigena-region.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gduar\Desktop\Academico\Docencia\UAI-AD\2026\05-inferencia\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A7C45842-FDA9-49EC-A91A-8BBB873BA7C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84F5C838-69EB-4FCF-B516-39A7D471E53A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{49FE5C17-3C81-4A07-8180-53D40FF6225F}"/>
+    <workbookView xWindow="2652" yWindow="2652" windowWidth="17280" windowHeight="9960" xr2:uid="{49FE5C17-3C81-4A07-8180-53D40FF6225F}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -108,9 +108,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="169" formatCode="[$-10C0A]#,##0;\-#,##0"/>
     <numFmt numFmtId="170" formatCode="[$-10409]#,##0;\(#,##0\)"/>
+    <numFmt numFmtId="173" formatCode="0.0%"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -199,7 +200,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
@@ -223,6 +224,7 @@
     <xf numFmtId="170" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -565,7 +567,7 @@
     <col min="1" max="1" width="34.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="46.8" x14ac:dyDescent="0.3">
@@ -817,7 +819,7 @@
       <c r="C17" s="8">
         <v>100745</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D17" s="9">
         <f t="shared" si="0"/>
         <v>0.29013846841034296</v>
       </c>
